--- a/gross_per_show_cutoff_comp.xlsx
+++ b/gross_per_show_cutoff_comp.xlsx
@@ -610,61 +610,61 @@
         <v>2024</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2179</v>
+        <v>2183</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>526905</v>
+        <v>526090</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>402971</v>
+        <v>409004</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>557884</v>
+        <v>556962</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>579991</v>
+        <v>583868</v>
       </c>
       <c r="L3" s="3" t="n">
         <v>66.73999999999999</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>78.93000000000001</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>7895.3</v>
+        <v>7883.3</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>5105.1</v>
+        <v>5163.8</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>17203924</v>
+        <v>17209148</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>2057364</v>
+        <v>2034531</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>1148126295.39</v>
+        <v>1148455418.34</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>162397440.67</v>
+        <v>161147449.99</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-0.2352</v>
+        <v>-0.2226</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.1826</v>
+        <v>0.1868</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>-0.3534</v>
+        <v>-0.345</v>
       </c>
     </row>
     <row r="4">
@@ -682,61 +682,61 @@
         <v>2025</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1222</v>
+        <v>1762</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>215</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1283</v>
+        <v>1848</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>231</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>483191</v>
+        <v>490136</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>486735</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>507311</v>
+        <v>514059</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>522957</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>66.63</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>71.55</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>7252.1</v>
+        <v>7200.2</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>6802.8</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>9304442</v>
+        <v>13305919</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>1571454</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>619933926.75</v>
+        <v>905771979.29</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>112435784.85</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>0.0073</v>
+        <v>-0.0069</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.0738</v>
+        <v>0.0511</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.062</v>
+        <v>-0.0552</v>
       </c>
     </row>
     <row r="5">
@@ -754,61 +754,61 @@
         <v>2024</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1196</v>
+        <v>1175</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1418</v>
+        <v>1397</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2755996</v>
+        <v>2795022</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>2799171</v>
+        <v>2806735</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3267560</v>
+        <v>3323102</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>4036573</v>
+        <v>4052828</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>114.08</v>
+        <v>114.15</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>103.42</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>24159.1</v>
+        <v>24486</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>27066.9</v>
+        <v>27137.9</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>34257660</v>
+        <v>34206996</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>9094469</v>
+        <v>9091204</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>3908001758.09</v>
+        <v>3904645316.26</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>940521596.52</v>
+        <v>940256059.4400001</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.0157</v>
+        <v>0.0042</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>-0.0934</v>
+        <v>-0.094</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.1204</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="6">
@@ -826,61 +826,61 @@
         <v>2025</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1071</v>
+        <v>1256</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1297</v>
+        <v>1542</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>3423655</v>
+        <v>3480178</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2743285</v>
+        <v>2754242</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4146107</v>
+        <v>4272639</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>3784614</v>
+        <v>3808334</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>125.2</v>
+        <v>126.17</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>109.05</v>
+        <v>109.14</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>27345.1</v>
+        <v>27582.6</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>25155.5</v>
+        <v>25235.6</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>35466592</v>
+        <v>42532303</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>8502550</v>
+        <v>8479155</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>4440480298.36</v>
+        <v>5366434218.17</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>927230484.65</v>
+        <v>925425166.05</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.1987</v>
+        <v>-0.2086</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.129</v>
+        <v>-0.135</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.0801</v>
+        <v>-0.0851</v>
       </c>
     </row>
     <row r="7">
@@ -898,58 +898,58 @@
         <v>2024</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6620</v>
+        <v>6635</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3043</v>
+        <v>3053</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8394</v>
+        <v>8409</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>3704</v>
+        <v>3715</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>743429</v>
+        <v>742458</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>654316</v>
+        <v>653507</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>942650</v>
+        <v>940970</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>796447</v>
+        <v>795211</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>96.37</v>
+        <v>96.31</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>87.23</v>
+        <v>87.19</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>7714.7</v>
+        <v>7709.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>7501.1</v>
+        <v>7495.4</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>64757113</v>
+        <v>64827758</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>27784259</v>
+        <v>27845238</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>6240346052.6</v>
+        <v>6243332824.07</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>2423587363.41</v>
+        <v>2427779069.04</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1199</v>
+        <v>-0.1198</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.0948</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V7" s="4" t="n">
         <v>-0.0277</v>
@@ -970,61 +970,61 @@
         <v>2025</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>5043</v>
+        <v>6174</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2882</v>
+        <v>2895</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>6222</v>
+        <v>7547</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3422</v>
+        <v>3438</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>710309</v>
+        <v>739971</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>745999</v>
+        <v>745776</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>876372</v>
+        <v>904529</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>885777</v>
+        <v>885657</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>91.56</v>
+        <v>93.42</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>89.06</v>
+        <v>89.05</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>7758.2</v>
+        <v>7920.6</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>8376.6</v>
+        <v>8374.9</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>48271765</v>
+        <v>59776482</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>28664858</v>
+        <v>28792794</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>4419545047.09</v>
+        <v>5584559137.76</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>2552809497.27</v>
+        <v>2563976658.58</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.0502</v>
+        <v>0.0078</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.0273</v>
+        <v>-0.0468</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0574</v>
       </c>
     </row>
     <row r="9">
@@ -1042,61 +1042,61 @@
         <v>2024</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>14921</v>
+        <v>14926</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7338</v>
+        <v>7346</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>18920</v>
+        <v>18925</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>10136</v>
+        <v>10149</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>109414</v>
+        <v>109401</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>105079</v>
+        <v>105031</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>138738</v>
+        <v>138712</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>145145</v>
+        <v>145107</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>69.3</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>70.68000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>1578.9</v>
+        <v>1578.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1486.8</v>
+        <v>1486.9</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>29873357</v>
+        <v>29878810</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>15069814</v>
+        <v>15091040</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>2070104627</v>
+        <v>2070408121.32</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1065076349.3</v>
+        <v>1065957660.89</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.0396</v>
+        <v>-0.0399</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.0199</v>
+        <v>0.0195</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.0583</v>
+        <v>-0.0582</v>
       </c>
     </row>
     <row r="10">
@@ -1114,61 +1114,61 @@
         <v>2025</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>12988</v>
+        <v>15256</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>6939</v>
+        <v>6960</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>16516</v>
+        <v>19172</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9229</v>
+        <v>9255</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>106224</v>
+        <v>106950</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>116670</v>
+        <v>116566</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>135079</v>
+        <v>134402</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>155174</v>
+        <v>155003</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>71.27</v>
+        <v>71.69</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>74.77</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1490.4</v>
+        <v>1491.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1560.5</v>
+        <v>1559.2</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>24616088</v>
+        <v>28600009</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>14401665</v>
+        <v>14430721</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1754402409.63</v>
+        <v>2050441567.86</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1076751621.04</v>
+        <v>1078817692.85</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.0983</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.0491</v>
+        <v>0.0428</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.047</v>
+        <v>0.0452</v>
       </c>
     </row>
     <row r="11">
@@ -1186,61 +1186,61 @@
         <v>2024</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>17326</v>
+        <v>17337</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>6711</v>
+        <v>6731</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>18028</v>
+        <v>18039</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>6923</v>
+        <v>6943</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>22457</v>
+        <v>22456</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>24654</v>
+        <v>24664</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>23367</v>
+        <v>23366</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>25433</v>
+        <v>25441</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>40.67</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42.03</v>
+        <v>42.01</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>552.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>586.6</v>
+        <v>587</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>9954961</v>
+        <v>9961097</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>4061049</v>
+        <v>4075837</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>404859604.74</v>
+        <v>405090517.49</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>170679499.04</v>
+        <v>171243237.16</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.0978</v>
+        <v>0.0983</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.0334</v>
+        <v>0.0329</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.0623</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="12">
@@ -1258,61 +1258,61 @@
         <v>2025</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>13157</v>
+        <v>15485</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5872</v>
+        <v>5902</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>13675</v>
+        <v>16070</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>6123</v>
+        <v>6153</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>22744</v>
+        <v>23398</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>25486</v>
+        <v>25458</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>23640</v>
+        <v>24282</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>26575</v>
+        <v>26541</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>42.36</v>
+        <v>42.89</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>44.51</v>
+        <v>44.47</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>536.9</v>
+        <v>545.6</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>572.6</v>
+        <v>572.4</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>7342375</v>
+        <v>8767354</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>3506236</v>
+        <v>3522150</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>311030239.57</v>
+        <v>376007352.81</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>156048472.59</v>
+        <v>156644525.95</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.1206</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.0508</v>
+        <v>0.0368</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.0665</v>
+        <v>0.0491</v>
       </c>
     </row>
     <row r="13">
@@ -1330,61 +1330,61 @@
         <v>2024</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2858</v>
+        <v>2879</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3235</v>
+        <v>3256</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>223698</v>
+        <v>223231</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>94587</v>
+        <v>93596</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>253206</v>
+        <v>252462</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>104740</v>
+        <v>103596</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>74</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>65.73</v>
+        <v>65.8</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>3022.8</v>
+        <v>3016.9</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1439</v>
+        <v>1422.5</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>9778818</v>
+        <v>9822979</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>1499438</v>
+        <v>1473755</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>723663931.14</v>
+        <v>726838645.23</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>98560036.27</v>
+        <v>96965845.17</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.5772</v>
+        <v>-0.5807</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1118</v>
+        <v>-0.1107</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.524</v>
+        <v>-0.5285</v>
       </c>
     </row>
     <row r="14">
@@ -1402,61 +1402,61 @@
         <v>2025</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2266</v>
+        <v>2787</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2738</v>
+        <v>3289</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>213959</v>
+        <v>240377</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>166908</v>
+        <v>168091</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>258526</v>
+        <v>283674</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>183444</v>
+        <v>184647</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>84.58</v>
+        <v>85.12</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>84.14</v>
+        <v>84</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2529.7</v>
+        <v>2823.9</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>1983.7</v>
+        <v>2001.1</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>6926326</v>
+        <v>9287843</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>1870623</v>
+        <v>1896998</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>585819024.85</v>
+        <v>790598561.03</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>157394668.05</v>
+        <v>159350346.79</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2199</v>
+        <v>-0.3007</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.0052</v>
+        <v>-0.0132</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2158</v>
+        <v>-0.2914</v>
       </c>
     </row>
     <row r="15">
@@ -1474,61 +1474,61 @@
         <v>2024</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>44979</v>
+        <v>45014</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>18546</v>
+        <v>18574</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>52174</v>
+        <v>52209</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>22544</v>
+        <v>22572</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>277822</v>
+        <v>277706</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>215615</v>
+        <v>215459</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>322264</v>
+        <v>322095</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>262095</v>
+        <v>261836</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>87.41</v>
+        <v>87.39</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>3178.3</v>
+        <v>3177.7</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>2642.2</v>
+        <v>2641</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>165825833</v>
+        <v>165906788</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>59566393</v>
+        <v>59611605</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>14495102268.96</v>
+        <v>14498770842.71</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>4860822285.21</v>
+        <v>4863349321.69</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.2239</v>
+        <v>-0.2241</v>
       </c>
       <c r="U15" s="4" t="n">
         <v>-0.0665</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1687</v>
+        <v>-0.1689</v>
       </c>
     </row>
     <row r="16">
@@ -1546,61 +1546,61 @@
         <v>2025</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>35747</v>
+        <v>42720</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>17011</v>
+        <v>17078</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>41731</v>
+        <v>49468</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>20286</v>
+        <v>20361</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>290700</v>
+        <v>304718</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>245621</v>
+        <v>245403</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>339363</v>
+        <v>352851</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>292909</v>
+        <v>292578</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>91.95</v>
+        <v>92.89</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>85.15000000000001</v>
+        <v>85.13</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>3161.4</v>
+        <v>3280.3</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2884.6</v>
+        <v>2882.6</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>131927588</v>
+        <v>162269910</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>58517386</v>
+        <v>58693272</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>12131210946.25</v>
+        <v>15073812816.92</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>4982670528.45</v>
+        <v>4996650175.07</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.1551</v>
+        <v>-0.1947</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.074</v>
+        <v>-0.0835</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.0876</v>
+        <v>-0.1212</v>
       </c>
     </row>
     <row r="17">
@@ -1690,61 +1690,61 @@
         <v>2025</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>567</v>
+        <v>839</v>
       </c>
       <c r="E18" s="3" t="n">
         <v>100</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>582</v>
+        <v>863</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>107</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>644699</v>
+        <v>657227</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>659837</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>661755</v>
+        <v>676028</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>706026</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>62.34</v>
+        <v>64.23</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>75.09999999999999</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>10341.3</v>
+        <v>10232.1</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>8785.9</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>6018643</v>
+        <v>8830288</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>940093</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>375214992.96</v>
+        <v>567187119.33</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>70602611.77</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.0235</v>
+        <v>0.004</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.2047</v>
+        <v>0.1692</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.1504</v>
+        <v>-0.1413</v>
       </c>
     </row>
     <row r="19">
@@ -1834,61 +1834,61 @@
         <v>2025</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>475</v>
+        <v>550</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>115</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>608</v>
+        <v>715</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>134</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4835934</v>
+        <v>5032853</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>4406591</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>6189996</v>
+        <v>6542709</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>5134637</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>139.16</v>
+        <v>139.07</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>116.17</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>34751.2</v>
+        <v>36189.4</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>37931.7</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>21128756</v>
+        <v>25875442</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>5082851</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>2940248153.25</v>
+        <v>3598489878.71</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>590483257.41</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.0888</v>
+        <v>-0.1244</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1652</v>
+        <v>-0.1647</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.0915</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="21">
@@ -1906,61 +1906,61 @@
         <v>2024</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1292130</v>
+        <v>1291141</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1064270</v>
+        <v>1063605</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1453259</v>
+        <v>1451993</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1191025</v>
+        <v>1191333</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>124.89</v>
+        <v>124.87</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>106.46</v>
+        <v>106.37</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>10345.9</v>
+        <v>10339.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>9997.1</v>
+        <v>9998.799999999999</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>24261146</v>
+        <v>24267505</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>9957088</v>
+        <v>9978785</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>3030045883.58</v>
+        <v>3030308654.1</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1060012477.96</v>
+        <v>1061477441.28</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1763</v>
+        <v>-0.1762</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.1476</v>
+        <v>-0.1482</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.0337</v>
+        <v>-0.033</v>
       </c>
     </row>
     <row r="22">
@@ -1978,61 +1978,61 @@
         <v>2025</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1238</v>
+        <v>1628</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1366</v>
+        <v>1804</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>912</v>
+        <v>917</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1169703</v>
+        <v>1176319</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1021224</v>
+        <v>1021694</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1290642</v>
+        <v>1303489</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>1187955</v>
+        <v>1187445</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>113.49</v>
+        <v>113.39</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>104.92</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>10306.6</v>
+        <v>10374.3</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>9733.5</v>
+        <v>9738.299999999999</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>14078858</v>
+        <v>18715247</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>8876951</v>
+        <v>8930011</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>1597814252.66</v>
+        <v>2122079543.41</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>931356730.85</v>
+        <v>936893847.36</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.1269</v>
+        <v>-0.1314</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.0755</v>
+        <v>-0.0747</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.0556</v>
+        <v>-0.0613</v>
       </c>
     </row>
     <row r="23">
@@ -2050,61 +2050,61 @@
         <v>2024</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2567</v>
+        <v>2573</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>175166</v>
+        <v>175053</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>142951</v>
+        <v>143047</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>218383</v>
+        <v>218116</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>184400</v>
+        <v>184572</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>76.86</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>73.42</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2279</v>
+        <v>2278.6</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1947.5</v>
+        <v>1948.3</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>5850221</v>
+        <v>5862865</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2200684</v>
+        <v>2199682</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>449651498.65</v>
+        <v>450410348.83</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>161534248.64</v>
+        <v>161500221.35</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.1839</v>
+        <v>-0.1828</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.045</v>
+        <v>-0.0443</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.1455</v>
+        <v>-0.145</v>
       </c>
     </row>
     <row r="24">
@@ -2122,61 +2122,61 @@
         <v>2025</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1445</v>
+        <v>1759</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1724</v>
+        <v>2096</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>175014</v>
+        <v>173280</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>160135</v>
+        <v>160628</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>208805</v>
+        <v>206478</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>217663</v>
+        <v>218130</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>78.02</v>
+        <v>77.61</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>78</v>
+        <v>78.05</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2243.3</v>
+        <v>2232.8</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>2053.1</v>
+        <v>2058</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3867497</v>
+        <v>4679903</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>2369274</v>
+        <v>2381100</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>301723490.9</v>
+        <v>363193937.19</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>184795796.81</v>
+        <v>185846612.46</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.073</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.0003</v>
+        <v>0.0057</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.0848</v>
+        <v>-0.07829999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -2194,25 +2194,25 @@
         <v>2024</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>796</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>815</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>40677</v>
+        <v>40664</v>
       </c>
       <c r="I25" s="3" t="n">
         <v>38872</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>41466</v>
+        <v>41452</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>39800</v>
@@ -2224,31 +2224,31 @@
         <v>47.88</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>874.9</v>
+        <v>874.7</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>811.8</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>1702607</v>
+        <v>1702966</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>661633</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>79158030.84999999</v>
+        <v>79172917.67</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>31680570.13</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.0444</v>
+        <v>-0.0441</v>
       </c>
       <c r="U25" s="4" t="n">
         <v>0.0299</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.0721</v>
+        <v>-0.07190000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2266,61 +2266,61 @@
         <v>2025</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1560</v>
+        <v>1858</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1596</v>
+        <v>1897</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>37527</v>
+        <v>39223</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>33244</v>
+        <v>33219</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>38393</v>
+        <v>40046</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>33804</v>
+        <v>33776</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>45.32</v>
+        <v>46.26</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>44.38</v>
+        <v>44.35</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>828.1</v>
+        <v>847.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>749.2</v>
+        <v>749</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>1321691</v>
+        <v>1608271</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>633796</v>
+        <v>635116</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>59893281.3</v>
+        <v>74405136.36</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>28124742.09</v>
+        <v>28169497.8</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.1141</v>
+        <v>-0.1531</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.0207</v>
+        <v>-0.0413</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.0953</v>
+        <v>-0.1165</v>
       </c>
     </row>
     <row r="27">
@@ -2338,61 +2338,61 @@
         <v>2024</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>374959</v>
+        <v>381291</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>108047</v>
+        <v>100613</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>410444</v>
+        <v>418310</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>155660</v>
+        <v>144470</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>71.34</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>57.66</v>
+        <v>56.94</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>5255.6</v>
+        <v>5331.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1873.8</v>
+        <v>1767</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1823697</v>
+        <v>1807429</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>318547</v>
+        <v>296850</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>130110611.08</v>
+        <v>129257709.56</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>18367935.39</v>
+        <v>16902972.07</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.7118</v>
+        <v>-0.7361</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.1918</v>
+        <v>-0.2037</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.6435</v>
+        <v>-0.6686</v>
       </c>
     </row>
     <row r="28">
@@ -2410,61 +2410,61 @@
         <v>2025</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>92</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>96</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>430875</v>
+        <v>522200</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>331759</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>491303</v>
+        <v>590110</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>346184</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>83.31999999999999</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>76.08</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>5171.4</v>
+        <v>5691.1</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>4360.9</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>967058</v>
+        <v>1434146</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>418650</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>80573624.66</v>
+        <v>131594446.52</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>31848888.86</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.23</v>
+        <v>-0.3647</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.1709</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.1567</v>
+        <v>-0.2337</v>
       </c>
     </row>
     <row r="29">
@@ -2482,28 +2482,28 @@
         <v>2024</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>7718</v>
+        <v>7719</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>8669</v>
+        <v>8670</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3362</v>
+        <v>3361</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>717407</v>
+        <v>717346</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>582117</v>
+        <v>582280</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>805805</v>
+        <v>805725</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>677424</v>
+        <v>677647</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>102.92</v>
@@ -2512,31 +2512,31 @@
         <v>98.67</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6970.5</v>
+        <v>6970</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>5899.6</v>
+        <v>5901</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>60426957</v>
+        <v>60430051</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>19834304</v>
+        <v>19833302</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>6219204526.72</v>
+        <v>6219388132.72</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1957077120.35</v>
+        <v>1957043093.06</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1886</v>
+        <v>-0.1883</v>
       </c>
       <c r="U29" s="4" t="n">
         <v>-0.0413</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.1536</v>
+        <v>-0.1534</v>
       </c>
     </row>
     <row r="30">
@@ -2554,61 +2554,61 @@
         <v>2025</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5449</v>
+        <v>6857</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2772</v>
+        <v>2782</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>6063</v>
+        <v>7627</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3249</v>
+        <v>3259</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>883303</v>
+        <v>899036</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>565470</v>
+        <v>565770</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>982835</v>
+        <v>999993</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>662775</v>
+        <v>662777</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>113.03</v>
+        <v>112.15</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>100.28</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7815</v>
+        <v>8016.7</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>5639.2</v>
+        <v>5642.2</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>47382503</v>
+        <v>61143297</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>18321615</v>
+        <v>18387821</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>5355467795.73</v>
+        <v>6856950061.52</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1837212027.79</v>
+        <v>1843844715.66</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.3598</v>
+        <v>-0.3707</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1128</v>
+        <v>-0.1058</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2784</v>
+        <v>-0.2962</v>
       </c>
     </row>
   </sheetData>
